--- a/elo/knapsack/excel365/fantasydf_falun_relay.xlsx
+++ b/elo/knapsack/excel365/fantasydf_falun_relay.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>name</t>
   </si>
@@ -40,67 +40,55 @@
     <t>place</t>
   </si>
   <si>
-    <t>ts_elo</t>
-  </si>
-  <si>
-    <t>relay_points</t>
-  </si>
-  <si>
-    <t>ts_points</t>
-  </si>
-  <si>
     <t>NORWAY I</t>
   </si>
   <si>
+    <t>NORWAY II</t>
+  </si>
+  <si>
+    <t>FRANCE I</t>
+  </si>
+  <si>
+    <t>SWEDEN I</t>
+  </si>
+  <si>
+    <t>ITALY I</t>
+  </si>
+  <si>
+    <t>GERMANY I</t>
+  </si>
+  <si>
     <t>FINLAND I</t>
   </si>
   <si>
-    <t>SWEDEN I</t>
-  </si>
-  <si>
-    <t>NORWAY II</t>
-  </si>
-  <si>
-    <t>GERMANY I</t>
-  </si>
-  <si>
     <t>UNITED STATES OF AMERICA I</t>
   </si>
   <si>
-    <t>FRANCE I</t>
-  </si>
-  <si>
-    <t>ITALY I</t>
-  </si>
-  <si>
     <t>GERMANY II</t>
   </si>
   <si>
+    <t>CANADA I</t>
+  </si>
+  <si>
+    <t>SWITZERLAND I</t>
+  </si>
+  <si>
+    <t>FINLAND II</t>
+  </si>
+  <si>
     <t>SWEDEN II</t>
   </si>
   <si>
-    <t>JAPAN I</t>
-  </si>
-  <si>
-    <t>FINLAND II</t>
-  </si>
-  <si>
-    <t>CANADA I</t>
-  </si>
-  <si>
-    <t>SWITZERLAND I</t>
-  </si>
-  <si>
-    <t>AUSTRIA I</t>
-  </si>
-  <si>
-    <t>ESTONIA I</t>
+    <t>ITALY II</t>
   </si>
   <si>
     <t>UNITED STATES OF AMERICA II</t>
   </si>
   <si>
-    <t>SWITZERLAND II</t>
+    <t>POLAND I</t>
+  </si>
+  <si>
+    <t>AUSTRALIA I</t>
   </si>
   <si>
     <t>mixed</t>
@@ -461,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,37 +477,28 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>8420150</v>
       </c>
       <c r="D2">
-        <v>22365</v>
+        <v>21706</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>265.2583038628309</v>
+        <v>68.97653368162733</v>
       </c>
       <c r="G2">
-        <v>7206.389266750914</v>
+        <v>6921.404526453294</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -527,660 +506,469 @@
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>3342.547372120952</v>
-      </c>
-      <c r="K2">
-        <v>132.6291519314154</v>
-      </c>
-      <c r="L2">
-        <v>132.6291519314154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>3181547</v>
+        <v>8420151</v>
       </c>
       <c r="D3">
-        <v>13524</v>
+        <v>7691</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>228.0845128723512</v>
+        <v>38.73078150253556</v>
       </c>
       <c r="G3">
-        <v>6931.910976373872</v>
+        <v>6491.641123547428</v>
       </c>
       <c r="H3">
-        <v>96.19118146110371</v>
+        <v>93.79080645751408</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3">
-        <v>3164.478801851436</v>
-      </c>
-      <c r="K3">
-        <v>116.9888514485856</v>
-      </c>
-      <c r="L3">
-        <v>111.0956614237656</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>3502077</v>
+        <v>3190590</v>
       </c>
       <c r="D4">
-        <v>17514</v>
+        <v>9281</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>201.1598550187308</v>
+        <v>22.64180545043045</v>
       </c>
       <c r="G4">
-        <v>6838.198270620121</v>
+        <v>6166.030485653899</v>
       </c>
       <c r="H4">
-        <v>94.89077008607396</v>
+        <v>89.08640525326341</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>2959.6519883979</v>
-      </c>
-      <c r="K4">
-        <v>111.930268392371</v>
-      </c>
-      <c r="L4">
-        <v>89.22958662635982</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>8420151</v>
+        <v>3502077</v>
       </c>
       <c r="D5">
-        <v>2920</v>
+        <v>19821</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>179.0195373868321</v>
+        <v>18.13363448694536</v>
       </c>
       <c r="G5">
-        <v>6423.030761314817</v>
+        <v>6049.064109908981</v>
       </c>
       <c r="H5">
-        <v>89.12966707126989</v>
+        <v>87.39648270505982</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
-      <c r="J5">
-        <v>2945.53302549304</v>
-      </c>
-      <c r="K5">
-        <v>91.18692436357915</v>
-      </c>
-      <c r="L5">
-        <v>87.83261302325296</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>3201057</v>
+        <v>210280</v>
       </c>
       <c r="D6">
-        <v>12415</v>
+        <v>11129</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>173.9481681592287</v>
+        <v>16.5959522263469</v>
       </c>
       <c r="G6">
-        <v>6415.025358318194</v>
+        <v>6004.986835744652</v>
       </c>
       <c r="H6">
-        <v>89.01857949744762</v>
+        <v>86.75965713019467</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6">
-        <v>2896.987223746593</v>
-      </c>
-      <c r="K6">
-        <v>90.81308603910935</v>
-      </c>
-      <c r="L6">
-        <v>83.13508212011934</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>3530978</v>
+        <v>3201057</v>
       </c>
       <c r="D7">
-        <v>14191</v>
+        <v>12977</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>157.8884058632958</v>
+        <v>15.75255089825229</v>
       </c>
       <c r="G7">
-        <v>6216.756366571523</v>
+        <v>5979.706391330123</v>
       </c>
       <c r="H7">
-        <v>86.26728499464507</v>
+        <v>86.3944069224094</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
-      <c r="J7">
-        <v>2820.117265872815</v>
-      </c>
-      <c r="K7">
-        <v>81.86119455328009</v>
-      </c>
-      <c r="L7">
-        <v>76.02721131001576</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>3190590</v>
+        <v>3181547</v>
       </c>
       <c r="D8">
-        <v>9078</v>
+        <v>14610</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>151.9116366750144</v>
+        <v>13.15586047066676</v>
       </c>
       <c r="G8">
-        <v>6185.85420016581</v>
+        <v>5896.032360552397</v>
       </c>
       <c r="H8">
-        <v>85.83846876973905</v>
+        <v>85.18548999726903</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8">
-        <v>2767.522098572808</v>
-      </c>
-      <c r="K8">
-        <v>80.51852315072401</v>
-      </c>
-      <c r="L8">
-        <v>71.39311352429036</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>210280</v>
+        <v>3530978</v>
       </c>
       <c r="D9">
-        <v>9415</v>
+        <v>14976</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>133.0203079488245</v>
+        <v>11.07350932043115</v>
       </c>
       <c r="G9">
-        <v>5749.839625006924</v>
+        <v>5821.017801720187</v>
       </c>
       <c r="H9">
-        <v>79.78807988538354</v>
+        <v>84.10168455654515</v>
       </c>
       <c r="I9">
         <v>8</v>
       </c>
-      <c r="J9">
-        <v>2751.080784855748</v>
-      </c>
-      <c r="K9">
-        <v>63.03819676427698</v>
-      </c>
-      <c r="L9">
-        <v>69.98211118454753</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>-2</v>
+        <v>3201197</v>
       </c>
       <c r="D10">
-        <v>1987</v>
+        <v>3209</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>125.1913775445514</v>
+        <v>6.85568081797953</v>
       </c>
       <c r="G10">
-        <v>5749.305031552587</v>
+        <v>5635.655097112547</v>
       </c>
       <c r="H10">
-        <v>79.78066155930443</v>
+        <v>81.42357632144356</v>
       </c>
       <c r="I10">
         <v>9</v>
       </c>
-      <c r="J10">
-        <v>2656.068447391509</v>
-      </c>
-      <c r="K10">
-        <v>63.01840440050939</v>
-      </c>
-      <c r="L10">
-        <v>62.17297314404203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>3100435</v>
       </c>
       <c r="D11">
-        <v>4130</v>
+        <v>7986</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>118.6070158623554</v>
+        <v>4.724324340826987</v>
       </c>
       <c r="G11">
-        <v>5687.912856160026</v>
+        <v>5512.645932111434</v>
       </c>
       <c r="H11">
-        <v>78.92874844276196</v>
+        <v>79.64634794921105</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11">
-        <v>2600</v>
-      </c>
-      <c r="K11">
-        <v>60.77151784900292</v>
-      </c>
-      <c r="L11">
-        <v>57.83549801335252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>3300639</v>
+        <v>3510719</v>
       </c>
       <c r="D12">
-        <v>1964</v>
+        <v>15159</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>112.5449996457881</v>
+        <v>4.456279134371505</v>
       </c>
       <c r="G12">
-        <v>5540.679154912503</v>
+        <v>5494.833199593291</v>
       </c>
       <c r="H12">
-        <v>76.8856489681494</v>
+        <v>79.38899075458295</v>
       </c>
       <c r="I12">
         <v>11</v>
       </c>
-      <c r="J12">
-        <v>2588.281804757816</v>
-      </c>
-      <c r="K12">
-        <v>55.59109048387172</v>
-      </c>
-      <c r="L12">
-        <v>56.95390916191641</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>3181548</v>
       </c>
       <c r="D13">
-        <v>4496</v>
+        <v>5369</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>108.9152877905538</v>
+        <v>2.628712238349888</v>
       </c>
       <c r="G13">
-        <v>5433.674510751539</v>
+        <v>5350.09957536898</v>
       </c>
       <c r="H13">
-        <v>75.40079101501792</v>
+        <v>77.29788881607978</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
-      <c r="J13">
-        <v>2587.666840600401</v>
-      </c>
-      <c r="K13">
-        <v>52.00740768636299</v>
-      </c>
-      <c r="L13">
-        <v>56.90788010419086</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>3100435</v>
+        <v>3502462</v>
       </c>
       <c r="D14">
-        <v>7227</v>
+        <v>6372</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>105.2171126628294</v>
+        <v>2.597747650108564</v>
       </c>
       <c r="G14">
-        <v>5366.691885611364</v>
+        <v>5347.162036318992</v>
       </c>
       <c r="H14">
-        <v>74.47130160415276</v>
+        <v>77.25544744397443</v>
       </c>
       <c r="I14">
         <v>13</v>
       </c>
-      <c r="J14">
-        <v>2567.028000305453</v>
-      </c>
-      <c r="K14">
-        <v>49.84040603701259</v>
-      </c>
-      <c r="L14">
-        <v>55.3767066258168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>3510719</v>
+        <v>210281</v>
       </c>
       <c r="D15">
-        <v>18338</v>
+        <v>1003</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>103.7607135318711</v>
+        <v>1.845296123007484</v>
       </c>
       <c r="G15">
-        <v>5333.162742160078</v>
+        <v>5267.666612678801</v>
       </c>
       <c r="H15">
-        <v>74.00603193566586</v>
+        <v>76.10690276151348</v>
       </c>
       <c r="I15">
         <v>14</v>
       </c>
-      <c r="J15">
-        <v>2561.666031267715</v>
-      </c>
-      <c r="K15">
-        <v>48.77749347926525</v>
-      </c>
-      <c r="L15">
-        <v>54.98322005260587</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>3050381</v>
+        <v>3530979</v>
       </c>
       <c r="D16">
-        <v>2355</v>
+        <v>3083</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>98.34337608261697</v>
+        <v>0.7602686054799977</v>
       </c>
       <c r="G16">
-        <v>5178.741234462872</v>
+        <v>5102.630316904583</v>
       </c>
       <c r="H16">
-        <v>71.86319032690513</v>
+        <v>73.72246915207111</v>
       </c>
       <c r="I16">
         <v>15</v>
       </c>
-      <c r="J16">
-        <v>2551.968613404985</v>
-      </c>
-      <c r="K16">
-        <v>44.06730013063437</v>
-      </c>
-      <c r="L16">
-        <v>54.27607595198261</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>3390288</v>
+        <v>3430319</v>
       </c>
       <c r="D17">
-        <v>5325</v>
+        <v>2876</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>94.0923131084416</v>
+        <v>0.2642607218094103</v>
       </c>
       <c r="G17">
-        <v>5109.988887820173</v>
+        <v>4964.809799985284</v>
       </c>
       <c r="H17">
-        <v>70.90914324316083</v>
+        <v>71.73124733585512</v>
       </c>
       <c r="I17">
         <v>16</v>
       </c>
-      <c r="J17">
-        <v>2520.565567611493</v>
-      </c>
-      <c r="K17">
-        <v>42.06663676436684</v>
-      </c>
-      <c r="L17">
-        <v>52.02567634407477</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>3530979</v>
+        <v>3040152</v>
       </c>
       <c r="D18">
-        <v>3102</v>
+        <v>962</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>89.21491709985665</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>5032.715397763498</v>
+        <v>4664.13714461816</v>
       </c>
       <c r="H18">
-        <v>69.83685187509387</v>
+        <v>67.38714847242406</v>
       </c>
       <c r="I18">
         <v>17</v>
-      </c>
-      <c r="J18">
-        <v>2481.756665787861</v>
-      </c>
-      <c r="K18">
-        <v>39.88767732920471</v>
-      </c>
-      <c r="L18">
-        <v>49.32723977065193</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19">
-        <v>3510720</v>
-      </c>
-      <c r="D19">
-        <v>3450</v>
-      </c>
-      <c r="E19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19">
-        <v>77.24603526171842</v>
-      </c>
-      <c r="G19">
-        <v>4962.526882218084</v>
-      </c>
-      <c r="H19">
-        <v>68.86287568608542</v>
-      </c>
-      <c r="I19">
-        <v>18</v>
-      </c>
-      <c r="J19">
-        <v>2324.020809426923</v>
-      </c>
-      <c r="K19">
-        <v>37.97156834611869</v>
-      </c>
-      <c r="L19">
-        <v>39.27446691559973</v>
       </c>
     </row>
   </sheetData>
